--- a/data.xlsx.xlsx
+++ b/data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D01186B-9648-4444-A59E-D93844756500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955AB79B-99FD-CE48-A992-D157F46AD0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="561">
   <si>
     <t>澤田七聖</t>
   </si>
@@ -1276,12 +1276,611 @@
   <si>
     <t>中島のの愛</t>
   </si>
+  <si>
+    <t>藤田セス和登</t>
+  </si>
+  <si>
+    <t>水嶋謙一郎</t>
+  </si>
+  <si>
+    <t>飯田歩夢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">戸田悠心 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>梅津俊壱</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小薗宗一郎</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中松英資</t>
+  </si>
+  <si>
+    <t>井上嘉希 </t>
+  </si>
+  <si>
+    <t>青木 七音 </t>
+  </si>
+  <si>
+    <t>藤原惺也 </t>
+  </si>
+  <si>
+    <t>市村心咲 </t>
+  </si>
+  <si>
+    <t>北川颯章 </t>
+  </si>
+  <si>
+    <t>西本 圭佑 </t>
+  </si>
+  <si>
+    <t>伊藤 悠木 </t>
+  </si>
+  <si>
+    <t>稲童丸怜 </t>
+  </si>
+  <si>
+    <t>山本みのり </t>
+  </si>
+  <si>
+    <t>小川 智由 </t>
+  </si>
+  <si>
+    <t>福元佑征 </t>
+  </si>
+  <si>
+    <t>山森瑛太 </t>
+  </si>
+  <si>
+    <t>井畑 奏人 </t>
+  </si>
+  <si>
+    <t>日下 遥斗 </t>
+  </si>
+  <si>
+    <t>森遥 来仁 </t>
+  </si>
+  <si>
+    <t>井上 玲音 </t>
+  </si>
+  <si>
+    <t>小猿 健太郎 </t>
+  </si>
+  <si>
+    <t>梶健留 </t>
+  </si>
+  <si>
+    <t>松本 悠聖 </t>
+  </si>
+  <si>
+    <t>橋目 龍之介</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ハシメ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🐉</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ノスケ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上野 圭太</t>
+  </si>
+  <si>
+    <t>中尾 優仁</t>
+  </si>
+  <si>
+    <t>濱中美侑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>五十嵐晃太</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>皆川 蒼斗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川手 智裕</t>
+  </si>
+  <si>
+    <t>吉海夏凪</t>
+  </si>
+  <si>
+    <t>平沼心結</t>
+  </si>
+  <si>
+    <t>長谷川結愛</t>
+  </si>
+  <si>
+    <t>斉藤 綾乃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>八藤丸颯太</t>
+  </si>
+  <si>
+    <t>細井琴葉</t>
+  </si>
+  <si>
+    <t>門田愛奈</t>
+  </si>
+  <si>
+    <t>上原　颯太郎</t>
+  </si>
+  <si>
+    <t>杉本 和香奈</t>
+  </si>
+  <si>
+    <t>村上遼介</t>
+  </si>
+  <si>
+    <t>大継悠日</t>
+  </si>
+  <si>
+    <t>前佛祐介</t>
+  </si>
+  <si>
+    <t>坂下　登大</t>
+  </si>
+  <si>
+    <t>竹内 凛太郎</t>
+  </si>
+  <si>
+    <t>井用みのり</t>
+  </si>
+  <si>
+    <t>田中颯人</t>
+  </si>
+  <si>
+    <t>掘出駿</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>片桐渚沙</t>
+  </si>
+  <si>
+    <t>日下 由菜</t>
+  </si>
+  <si>
+    <t>藤田智樹</t>
+  </si>
+  <si>
+    <t>高橋碧</t>
+  </si>
+  <si>
+    <t>石田克希</t>
+  </si>
+  <si>
+    <t>五味駿太朗</t>
+  </si>
+  <si>
+    <t>苅谷 美咲</t>
+  </si>
+  <si>
+    <t>森中啓仁</t>
+  </si>
+  <si>
+    <t>徳田拓夢</t>
+  </si>
+  <si>
+    <t>上野あゆ美</t>
+  </si>
+  <si>
+    <t>井出 駿人</t>
+  </si>
+  <si>
+    <t>伊藤 胡花</t>
+  </si>
+  <si>
+    <t>池尻煌人</t>
+  </si>
+  <si>
+    <t>石川蒼真</t>
+  </si>
+  <si>
+    <t>藤田洸太</t>
+  </si>
+  <si>
+    <t>美濃昂幸</t>
+  </si>
+  <si>
+    <t>松井蓮太郎</t>
+  </si>
+  <si>
+    <t>宮田 櫂</t>
+  </si>
+  <si>
+    <t>森本詩史</t>
+  </si>
+  <si>
+    <t>越野 紗良</t>
+  </si>
+  <si>
+    <t>久保田 航生</t>
+  </si>
+  <si>
+    <t>矢野天心</t>
+  </si>
+  <si>
+    <t>前田旺佑</t>
+  </si>
+  <si>
+    <t>村井 大和</t>
+  </si>
+  <si>
+    <t>安田 悠乃</t>
+  </si>
+  <si>
+    <t>下田 湧生</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>浅川瞬生</t>
+  </si>
+  <si>
+    <t>藤川 結灯</t>
+  </si>
+  <si>
+    <t>竹末 亘志</t>
+  </si>
+  <si>
+    <t>藤谷沙希</t>
+  </si>
+  <si>
+    <t>青木悠鈍</t>
+  </si>
+  <si>
+    <t>小曽戸大聖</t>
+  </si>
+  <si>
+    <t>前川 大和</t>
+  </si>
+  <si>
+    <t>下堂 聖真</t>
+  </si>
+  <si>
+    <t>柴原貴橙</t>
+  </si>
+  <si>
+    <t>木場優征</t>
+  </si>
+  <si>
+    <t>太田悠佑</t>
+  </si>
+  <si>
+    <t>木村圭都</t>
+  </si>
+  <si>
+    <t>本郷 隆太</t>
+  </si>
+  <si>
+    <t>三崎淳平</t>
+  </si>
+  <si>
+    <t>羽山 和希</t>
+  </si>
+  <si>
+    <t>津田 翔馬</t>
+  </si>
+  <si>
+    <t>香山諒太</t>
+  </si>
+  <si>
+    <t>長嶋 優衣</t>
+  </si>
+  <si>
+    <t>高木柚</t>
+  </si>
+  <si>
+    <t>及川 智大</t>
+  </si>
+  <si>
+    <t>山中  雅貴</t>
+  </si>
+  <si>
+    <t>山本賢汰</t>
+  </si>
+  <si>
+    <t>吉田 和生</t>
+  </si>
+  <si>
+    <t>倉橋一葉</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>八鍬 莉空</t>
+  </si>
+  <si>
+    <t>橋本 解</t>
+  </si>
+  <si>
+    <t>サンティ</t>
+  </si>
+  <si>
+    <t>梅本 夏帆</t>
+  </si>
+  <si>
+    <t>舟橋千隼</t>
+  </si>
+  <si>
+    <t>水野 颯仁</t>
+  </si>
+  <si>
+    <t>水口 諦</t>
+  </si>
+  <si>
+    <t>越智 太靖</t>
+  </si>
+  <si>
+    <t>小林 咲登</t>
+  </si>
+  <si>
+    <t>赤壁朋果</t>
+  </si>
+  <si>
+    <t>木村 駿杜</t>
+  </si>
+  <si>
+    <t>今井千瑛</t>
+  </si>
+  <si>
+    <t>窪田 莉子</t>
+  </si>
+  <si>
+    <t>中島咲桜</t>
+  </si>
+  <si>
+    <t>コリア</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>石崎 脩也</t>
+  </si>
+  <si>
+    <t>藤田彩香</t>
+  </si>
+  <si>
+    <t>相川 翔太郎</t>
+  </si>
+  <si>
+    <t>細岡大起</t>
+  </si>
+  <si>
+    <t>内田 雄貴</t>
+  </si>
+  <si>
+    <t>山﨑 彰大</t>
+  </si>
+  <si>
+    <t>前波花香</t>
+  </si>
+  <si>
+    <t>林田 一真</t>
+  </si>
+  <si>
+    <t>星川快鋳</t>
+  </si>
+  <si>
+    <t>山本 敦</t>
+  </si>
+  <si>
+    <t>西村大</t>
+  </si>
+  <si>
+    <t>成田惺真</t>
+  </si>
+  <si>
+    <t>能勢 陸斗</t>
+  </si>
+  <si>
+    <t>古川桃子</t>
+  </si>
+  <si>
+    <t>蒔田 大椰</t>
+  </si>
+  <si>
+    <t>村上 律</t>
+  </si>
+  <si>
+    <t>奥村知隼</t>
+  </si>
+  <si>
+    <t>石田 歩夢</t>
+  </si>
+  <si>
+    <t>小林咲</t>
+  </si>
+  <si>
+    <t>篠原 大悟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長谷 悠生 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">前川 大祐 </t>
+  </si>
+  <si>
+    <t>相坂 明里</t>
+  </si>
+  <si>
+    <t>松岡 健太郎</t>
+  </si>
+  <si>
+    <t>小林翔大</t>
+  </si>
+  <si>
+    <t>熊谷蘭武</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奥野智貴 </t>
+  </si>
+  <si>
+    <t>山中萌衣</t>
+  </si>
+  <si>
+    <t>中西倫子</t>
+  </si>
+  <si>
+    <t>瀧口隼</t>
+  </si>
+  <si>
+    <t>若松 咲月</t>
+  </si>
+  <si>
+    <t>伊藤 大晴</t>
+  </si>
+  <si>
+    <t>向所杏笑</t>
+  </si>
+  <si>
+    <t>田畑鷹悠</t>
+  </si>
+  <si>
+    <t>中野睦斗</t>
+  </si>
+  <si>
+    <t>西下洸太朗</t>
+  </si>
+  <si>
+    <t>渡辺柊有</t>
+  </si>
+  <si>
+    <t>山口翔雅</t>
+  </si>
+  <si>
+    <t>橋本春</t>
+  </si>
+  <si>
+    <t>平岡陸</t>
+  </si>
+  <si>
+    <t>大西勇毅</t>
+  </si>
+  <si>
+    <t>逢坂柊真</t>
+  </si>
+  <si>
+    <t>有田駈</t>
+  </si>
+  <si>
+    <t>廣田昇大</t>
+  </si>
+  <si>
+    <t>坂井康介</t>
+  </si>
+  <si>
+    <t>船富 遥斗</t>
+  </si>
+  <si>
+    <t>岡田 蒼介</t>
+  </si>
+  <si>
+    <t>石山詢人</t>
+  </si>
+  <si>
+    <t>杉本優太郎</t>
+  </si>
+  <si>
+    <t>真木洋斗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">増井 一太 </t>
+  </si>
+  <si>
+    <t>佐野 智優希</t>
+  </si>
+  <si>
+    <t>関隼太郎</t>
+  </si>
+  <si>
+    <t>前地遼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">笠井 遥紀 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">土井 翔太郎 </t>
+  </si>
+  <si>
+    <t>早川柊</t>
+  </si>
+  <si>
+    <t>木村晴樹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石田 迅 </t>
+  </si>
+  <si>
+    <t>伊藤 鴻甫</t>
+  </si>
+  <si>
+    <t>中野蒼司</t>
+  </si>
+  <si>
+    <t>野島大輝</t>
+  </si>
+  <si>
+    <t>鈎慈玖</t>
+  </si>
+  <si>
+    <t>障害物競走・赤団</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ショウガイブツ </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">キョウソウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アカダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害物競走・青団</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ショウガイブツキョウソウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害物競走・黄団</t>
+    <rPh sb="0" eb="5">
+      <t xml:space="preserve">ショウガイブツキョウソウ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障害物競走・黒団</t>
+    <rPh sb="0" eb="5">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">クロダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1343,6 +1942,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1352,7 +1974,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1493,13 +2115,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1557,11 +2194,73 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="46">
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
@@ -1590,6 +2289,17 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
@@ -1601,8 +2311,345 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1988,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E04C86-53A8-4C49-AB0F-61EBA36494D7}">
-  <dimension ref="A1:C365"/>
+  <dimension ref="A1:C553"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:3" ht="21" thickBot="1">
@@ -4953,37 +6000,1543 @@
         <v>378</v>
       </c>
     </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B366" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B367" s="19" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B368" s="19" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B369" s="19" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B370" s="19" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B371" s="19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B372" s="19" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B373" s="19" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B374" s="19" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B375" s="19" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B376" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B377" s="19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B378" s="19" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B379" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B380" s="19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B381" s="19" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B382" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B383" s="19" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B384" s="19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B385" s="19" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B386" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B387" s="19" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B388" s="19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B389" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B390" s="19" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B391" s="20" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B392" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B393" s="20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B394" s="20" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B395" s="20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B396" s="20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B397" s="20" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B398" s="20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B399" s="20" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B400" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B401" s="21" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B402" s="21" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B403" s="21" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B404" s="21" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B405" s="21" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B406" s="21" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B407" s="21" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B408" s="21" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B409" s="21" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="B410" s="21" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B411" s="21" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B412" s="21" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B413" s="21" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B414" s="21" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B415" s="21" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B416" s="21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B417" s="21" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B418" s="21" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B419" s="21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B420" s="21" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B421" s="21" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B422" s="21" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B423" s="21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B424" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B425" s="21" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B426" s="22" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B427" s="22" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B428" s="22" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B429" s="22" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B430" s="22" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B431" s="22" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B432" s="20" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B433" s="22" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B434" s="22" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B435" s="22" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B436" s="22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B437" s="22" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B438" s="22" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B439" s="22" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B440" s="22" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B441" s="21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B442" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B443" s="21" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B444" s="21" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B445" s="21" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B446" s="21" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B447" s="21" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B448" s="21" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B449" s="21" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B450" s="21" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B451" s="21" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B452" s="21" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B453" s="21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B454" s="21" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="B455" s="21" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B456" s="21" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B457" s="21" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B458" s="21" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B459" s="21" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B460" s="21" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B461" s="21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B462" s="21" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B463" s="21" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B464" s="21" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B465" s="21" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B466" s="21" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B467" s="21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B468" s="21" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B469" s="21" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B470" s="21" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B471" s="21" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B472" s="21" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B473" s="21" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B474" s="21" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B475" s="21" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B476" s="21" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B477" s="21" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B478" s="21" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B479" s="21" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B480" s="21" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B481" s="21" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B482" s="21" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B483" s="21" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B484" s="21" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B485" s="21" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B486" s="21" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B487" s="21" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B488" s="21" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B489" s="21" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B490" s="21" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B491" s="21" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B492" s="21" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B493" s="21" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B494" s="21" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B495" s="21" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B496" s="21" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B497" s="21" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B498" s="21" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B499" s="21" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B500" s="21" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B501" s="21" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B502" s="21" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B503" s="21" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B504" s="21" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B505" s="21" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B506" s="21" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B507" s="21" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B508" s="21" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B509" s="21" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B510" s="21" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B511" s="21" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B512" s="21" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B513" s="21" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B514" s="21" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B515" s="21" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B516" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B517" s="22" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B518" s="22" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B519" s="22" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B520" s="22" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B521" s="22" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B522" s="22" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B523" s="22" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B524" s="22" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B525" s="22" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B526" s="21" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B527" s="21" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B528" s="21" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B529" s="21" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B530" s="21" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B531" s="21" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B532" s="21" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B533" s="21" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B534" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B535" s="21" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B536" s="21" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B537" s="21" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B538" s="21" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B539" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B540" s="21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B541" s="21" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B542" s="21" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B543" s="21" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B544" s="21" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="B545" s="21" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="B546" s="23"/>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="B547" s="23"/>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="B548" s="23"/>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="B549" s="23"/>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="B550" s="23"/>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="B551" s="23"/>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="B552" s="23"/>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="B553" s="23"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B2:B344">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="38" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="39" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="40" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="41" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="41" priority="42">
       <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C21 C43:C63">
-    <cfRule type="cellIs" dxfId="3" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="101" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="102" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="103" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="104" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="64" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B401:B425">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B441:B515">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B526:B545">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx.xlsx
+++ b/data.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m2610025/Desktop/チェックイン/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955AB79B-99FD-CE48-A992-D157F46AD0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855C53DC-7304-9E46-9332-8C5A3124B119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{348E8972-E72E-5A4B-9183-B2C2B4112549}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="840">
   <si>
     <t>澤田七聖</t>
   </si>
@@ -1874,6 +1874,902 @@
       <t xml:space="preserve">クロダン </t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>団選抜リレー・赤団</t>
+  </si>
+  <si>
+    <t>岡田 理瑚</t>
+  </si>
+  <si>
+    <t>向井瑠海</t>
+  </si>
+  <si>
+    <t>中村滉志</t>
+  </si>
+  <si>
+    <t>岩本雪愛</t>
+  </si>
+  <si>
+    <t>岡本夏凛</t>
+  </si>
+  <si>
+    <t>中川結葵</t>
+  </si>
+  <si>
+    <t>根岸璃衣</t>
+  </si>
+  <si>
+    <t>井上栞那</t>
+  </si>
+  <si>
+    <t>堀川琉快</t>
+  </si>
+  <si>
+    <t>久保快翔</t>
+  </si>
+  <si>
+    <t>谷口楓</t>
+  </si>
+  <si>
+    <t>田内莉琴</t>
+  </si>
+  <si>
+    <t>村嶋彩日</t>
+  </si>
+  <si>
+    <t>三品遼音</t>
+  </si>
+  <si>
+    <t>神谷 幸輝</t>
+  </si>
+  <si>
+    <t>大西功都</t>
+  </si>
+  <si>
+    <t>辻柚香</t>
+  </si>
+  <si>
+    <t>西村太一</t>
+  </si>
+  <si>
+    <t>岸本大暉</t>
+  </si>
+  <si>
+    <t>由井陽斗</t>
+  </si>
+  <si>
+    <t>小薗宗一郎</t>
+  </si>
+  <si>
+    <t>岡本伊織</t>
+  </si>
+  <si>
+    <t>福永舞衣</t>
+  </si>
+  <si>
+    <t>中村謙吾</t>
+  </si>
+  <si>
+    <t>皆川蒼斗</t>
+  </si>
+  <si>
+    <t>熊谷 莉有</t>
+  </si>
+  <si>
+    <t>谷本真子</t>
+  </si>
+  <si>
+    <t>上之薗香帆</t>
+  </si>
+  <si>
+    <t>中林嶺佳</t>
+  </si>
+  <si>
+    <t>熊田結彩</t>
+  </si>
+  <si>
+    <t>奥村紗代</t>
+  </si>
+  <si>
+    <t>北川颯章</t>
+  </si>
+  <si>
+    <t>廣政孝太郎</t>
+  </si>
+  <si>
+    <t>中山萌衣</t>
+  </si>
+  <si>
+    <t>常峰祗園</t>
+  </si>
+  <si>
+    <t>片山陽</t>
+  </si>
+  <si>
+    <t>宇野宏紀</t>
+  </si>
+  <si>
+    <t>廣瀬 宗成</t>
+  </si>
+  <si>
+    <t>木村陸</t>
+  </si>
+  <si>
+    <t>永原拓真</t>
+  </si>
+  <si>
+    <t>濱田陸駆</t>
+  </si>
+  <si>
+    <t>吉岡将斗</t>
+  </si>
+  <si>
+    <t>松田一求</t>
+  </si>
+  <si>
+    <t>安原仁隆</t>
+  </si>
+  <si>
+    <t>石岡春蔵</t>
+  </si>
+  <si>
+    <t>栄口結愛</t>
+  </si>
+  <si>
+    <t>秦愛咲</t>
+  </si>
+  <si>
+    <t>小笠原啓太</t>
+  </si>
+  <si>
+    <t>足立晴太</t>
+  </si>
+  <si>
+    <t>団選抜リレー・青団</t>
+  </si>
+  <si>
+    <t>徳井凌太</t>
+  </si>
+  <si>
+    <t>日下由菜</t>
+  </si>
+  <si>
+    <t>片本真佳</t>
+  </si>
+  <si>
+    <t>奥野陽葵</t>
+  </si>
+  <si>
+    <t>林桃叶</t>
+  </si>
+  <si>
+    <t>渡邉煌士</t>
+  </si>
+  <si>
+    <t>山村王</t>
+  </si>
+  <si>
+    <t>川岡熙平</t>
+  </si>
+  <si>
+    <t>浅見陽香</t>
+  </si>
+  <si>
+    <t>井用あかり</t>
+  </si>
+  <si>
+    <t>藤井 彩友佳</t>
+  </si>
+  <si>
+    <t>中谷颯真</t>
+  </si>
+  <si>
+    <t>福嶋隼都</t>
+  </si>
+  <si>
+    <t>杉本陽</t>
+  </si>
+  <si>
+    <t>青木悠純</t>
+  </si>
+  <si>
+    <t>小島惟愛</t>
+  </si>
+  <si>
+    <t>Miki Schwarz</t>
+  </si>
+  <si>
+    <t>中嶋健登</t>
+  </si>
+  <si>
+    <t>橋本花凛</t>
+  </si>
+  <si>
+    <t>福井駿斗</t>
+  </si>
+  <si>
+    <t>谷本瑛汰</t>
+  </si>
+  <si>
+    <t>朝日千尋</t>
+  </si>
+  <si>
+    <t>丹野 凛緒</t>
+  </si>
+  <si>
+    <t>福田明里</t>
+  </si>
+  <si>
+    <t>岩永星南</t>
+  </si>
+  <si>
+    <t>田中健琉</t>
+  </si>
+  <si>
+    <t>木村真結奈</t>
+  </si>
+  <si>
+    <t>堀出駿</t>
+  </si>
+  <si>
+    <t>石田克季</t>
+  </si>
+  <si>
+    <t>上妻笑之祐</t>
+  </si>
+  <si>
+    <t>中田裕衣可</t>
+  </si>
+  <si>
+    <t>中前琴葉</t>
+  </si>
+  <si>
+    <t>安田悠乃</t>
+  </si>
+  <si>
+    <t>本郷隆太</t>
+  </si>
+  <si>
+    <t>岡田莉央</t>
+  </si>
+  <si>
+    <t>フースティング杏奈</t>
+  </si>
+  <si>
+    <t>木山凌汰</t>
+  </si>
+  <si>
+    <t>門田悠希</t>
+  </si>
+  <si>
+    <t>比木思結</t>
+  </si>
+  <si>
+    <t>兼平和季</t>
+  </si>
+  <si>
+    <t>岩崎航大</t>
+  </si>
+  <si>
+    <t>角田優斗</t>
+  </si>
+  <si>
+    <t>大林孝太朗</t>
+  </si>
+  <si>
+    <t>滝川康大</t>
+  </si>
+  <si>
+    <t>籔内梨琴</t>
+  </si>
+  <si>
+    <t>青木陽翔</t>
+  </si>
+  <si>
+    <t>大前 耀太郎</t>
+  </si>
+  <si>
+    <t>団選抜リレー・黄団</t>
+  </si>
+  <si>
+    <t>服部慶大</t>
+  </si>
+  <si>
+    <t>岡本菜優</t>
+  </si>
+  <si>
+    <t>田畑颯吾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森口侑大 </t>
+  </si>
+  <si>
+    <t>竹中菜都希</t>
+  </si>
+  <si>
+    <t>宇野吏蘭</t>
+  </si>
+  <si>
+    <t>水口果音</t>
+  </si>
+  <si>
+    <t>村上尚哉</t>
+  </si>
+  <si>
+    <t>小川瑛太郎</t>
+  </si>
+  <si>
+    <t>下堂真緒</t>
+  </si>
+  <si>
+    <t>鳥居幹太</t>
+  </si>
+  <si>
+    <t>齋藤夢</t>
+  </si>
+  <si>
+    <t>門野澪良</t>
+  </si>
+  <si>
+    <t>長岡克興</t>
+  </si>
+  <si>
+    <t>倉橋一葉</t>
+  </si>
+  <si>
+    <t>土渕海</t>
+  </si>
+  <si>
+    <t>手塚愛結</t>
+  </si>
+  <si>
+    <t>杉山拓也</t>
+  </si>
+  <si>
+    <t>松井簾太朗</t>
+  </si>
+  <si>
+    <t>小笠原羚斗</t>
+  </si>
+  <si>
+    <t>小早川珀瑛</t>
+  </si>
+  <si>
+    <t>森永徳真</t>
+  </si>
+  <si>
+    <t>上野今日香</t>
+  </si>
+  <si>
+    <t>山崎聖流</t>
+  </si>
+  <si>
+    <t>森杉優輝</t>
+  </si>
+  <si>
+    <t>佐々木菜那</t>
+  </si>
+  <si>
+    <t>髙橋暖</t>
+  </si>
+  <si>
+    <t>河上桜輔</t>
+  </si>
+  <si>
+    <t>山中七海</t>
+  </si>
+  <si>
+    <t>石崎脩也</t>
+  </si>
+  <si>
+    <t>木村啓士朗</t>
+  </si>
+  <si>
+    <t>西村大輔</t>
+  </si>
+  <si>
+    <t>岡野志栞</t>
+  </si>
+  <si>
+    <t>坂上美依</t>
+  </si>
+  <si>
+    <t>西龍生</t>
+  </si>
+  <si>
+    <t>福島莉子</t>
+  </si>
+  <si>
+    <t>長谷川結子</t>
+  </si>
+  <si>
+    <t>木村彩夢</t>
+  </si>
+  <si>
+    <t>三村真由</t>
+  </si>
+  <si>
+    <t>長谷川大雅</t>
+  </si>
+  <si>
+    <t>宮本あん</t>
+  </si>
+  <si>
+    <t>西崎蓮</t>
+  </si>
+  <si>
+    <t>川西陽翔</t>
+  </si>
+  <si>
+    <t>元好拓真</t>
+  </si>
+  <si>
+    <t>山森 幹太</t>
+  </si>
+  <si>
+    <t>梶郁斗</t>
+  </si>
+  <si>
+    <t>辻陽菜</t>
+  </si>
+  <si>
+    <t>乾莉央</t>
+  </si>
+  <si>
+    <t>松原幸輝</t>
+  </si>
+  <si>
+    <t>増田遥哉</t>
+  </si>
+  <si>
+    <t>団選抜リレー・黒団</t>
+  </si>
+  <si>
+    <t>山西瑛人</t>
+  </si>
+  <si>
+    <t>島津柚花</t>
+  </si>
+  <si>
+    <t>薬師蓮</t>
+  </si>
+  <si>
+    <t>瀬戸口桜</t>
+  </si>
+  <si>
+    <t>下村圭吾</t>
+  </si>
+  <si>
+    <t>小森蓮生</t>
+  </si>
+  <si>
+    <t>上田芽愛</t>
+  </si>
+  <si>
+    <t>小山明日香</t>
+  </si>
+  <si>
+    <t>茶木陽良里</t>
+  </si>
+  <si>
+    <t>藤原拓海</t>
+  </si>
+  <si>
+    <t>本田胡桃</t>
+  </si>
+  <si>
+    <t>森玄親</t>
+  </si>
+  <si>
+    <t>前川綾音</t>
+  </si>
+  <si>
+    <t>稲ヶ部心夢</t>
+  </si>
+  <si>
+    <t xml:space="preserve">野中悠翔 </t>
+  </si>
+  <si>
+    <t>松井駿典</t>
+  </si>
+  <si>
+    <t>金岡大輔</t>
+  </si>
+  <si>
+    <t>原田唯菜</t>
+  </si>
+  <si>
+    <t>今井寛太</t>
+  </si>
+  <si>
+    <t>大崎真之介</t>
+  </si>
+  <si>
+    <t>藤原梨津</t>
+  </si>
+  <si>
+    <t>西川湊太</t>
+  </si>
+  <si>
+    <t>土屋遼人</t>
+  </si>
+  <si>
+    <t>松本寧々</t>
+  </si>
+  <si>
+    <t>小川二葉</t>
+  </si>
+  <si>
+    <t>駒井絵理奈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角恵里奈 </t>
+  </si>
+  <si>
+    <t>安澤秀哉</t>
+  </si>
+  <si>
+    <t>辻陽香</t>
+  </si>
+  <si>
+    <t>谷陽依</t>
+  </si>
+  <si>
+    <t>青木一悟</t>
+  </si>
+  <si>
+    <t>松尾亮佑</t>
+  </si>
+  <si>
+    <t>龍華天花</t>
+  </si>
+  <si>
+    <t>二村沙紀</t>
+  </si>
+  <si>
+    <t>門田悠佑</t>
+  </si>
+  <si>
+    <t>西山瑚々</t>
+  </si>
+  <si>
+    <t xml:space="preserve">丸山大海 </t>
+  </si>
+  <si>
+    <t>河村羽桜</t>
+  </si>
+  <si>
+    <t>中村海音</t>
+  </si>
+  <si>
+    <t>堀池梨央</t>
+  </si>
+  <si>
+    <t>高西真聖</t>
+  </si>
+  <si>
+    <t>夢田翔正</t>
+  </si>
+  <si>
+    <t>鈴木陽也</t>
+  </si>
+  <si>
+    <t>男子棒取り・赤団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アカダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>川橋巧</t>
+  </si>
+  <si>
+    <t>豊島詢大</t>
+  </si>
+  <si>
+    <t>森戸鳳紀</t>
+  </si>
+  <si>
+    <t>谷龍風</t>
+  </si>
+  <si>
+    <t>木村悠希</t>
+  </si>
+  <si>
+    <t>小西由人</t>
+  </si>
+  <si>
+    <t>曽田佑亮</t>
+  </si>
+  <si>
+    <t>亀井勇杜</t>
+  </si>
+  <si>
+    <t>後藤大登</t>
+  </si>
+  <si>
+    <t>坂下登大</t>
+  </si>
+  <si>
+    <t>藤堂正輝</t>
+  </si>
+  <si>
+    <t>川尻悠生</t>
+  </si>
+  <si>
+    <t>前田大輔</t>
+  </si>
+  <si>
+    <t>的場駿士</t>
+  </si>
+  <si>
+    <t>林涼太</t>
+  </si>
+  <si>
+    <t>本田大翔</t>
+  </si>
+  <si>
+    <t>速水竣悟</t>
+  </si>
+  <si>
+    <t>植木蒼馬</t>
+  </si>
+  <si>
+    <t>三崎陽太</t>
+  </si>
+  <si>
+    <t>中村仁太朗</t>
+  </si>
+  <si>
+    <t>橋本竜成</t>
+  </si>
+  <si>
+    <t>男子棒取り・青団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太田亮ノ佑</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>万代悠羽</t>
+  </si>
+  <si>
+    <t>岩切音和</t>
+  </si>
+  <si>
+    <t>山田航大</t>
+  </si>
+  <si>
+    <t>山田晃誠</t>
+  </si>
+  <si>
+    <t>森健悟</t>
+  </si>
+  <si>
+    <t>山林心太朗</t>
+  </si>
+  <si>
+    <t>鳥本瑛斗</t>
+  </si>
+  <si>
+    <t>岩井翔大</t>
+  </si>
+  <si>
+    <t>前田真甫</t>
+  </si>
+  <si>
+    <t>中西巧実</t>
+  </si>
+  <si>
+    <t>青柴生</t>
+  </si>
+  <si>
+    <t>浦野亘輝</t>
+  </si>
+  <si>
+    <t>大川寛輔</t>
+  </si>
+  <si>
+    <t>飯田統維</t>
+  </si>
+  <si>
+    <t>細井瑛仁</t>
+  </si>
+  <si>
+    <t>島田光祐</t>
+  </si>
+  <si>
+    <t>帯刀亮真</t>
+  </si>
+  <si>
+    <t>山手悠生</t>
+  </si>
+  <si>
+    <t>竹田和貴</t>
+  </si>
+  <si>
+    <t>中川一輝</t>
+  </si>
+  <si>
+    <t>松田太志</t>
+  </si>
+  <si>
+    <t>杉本龍之祐</t>
+  </si>
+  <si>
+    <t>村上煌明</t>
+  </si>
+  <si>
+    <t>男子棒取り・黄団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>🌲</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>國定龍</t>
+  </si>
+  <si>
+    <t>奥村 航平</t>
+  </si>
+  <si>
+    <t>上城戸翔太</t>
+  </si>
+  <si>
+    <t>谷口善夕</t>
+  </si>
+  <si>
+    <t>小倉聡介</t>
+  </si>
+  <si>
+    <t>北村理</t>
+  </si>
+  <si>
+    <t>北川陸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辻健士朗 </t>
+  </si>
+  <si>
+    <t>矢谷太智</t>
+  </si>
+  <si>
+    <t>福澤蒼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">西崎蓮 </t>
+  </si>
+  <si>
+    <t>藤澤久眞</t>
+  </si>
+  <si>
+    <t>大堤永翔</t>
+  </si>
+  <si>
+    <t>本持諒也</t>
+  </si>
+  <si>
+    <t>穴見幸樹</t>
+  </si>
+  <si>
+    <t>伊藤隼一郎</t>
+  </si>
+  <si>
+    <t>森雄聖</t>
+  </si>
+  <si>
+    <t>男子棒取り・黒団</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ダンシ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">ボウ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>🪿</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t xml:space="preserve">クロ </t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">アオダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>児島遼哉</t>
+  </si>
+  <si>
+    <t>浅井健壱</t>
+  </si>
+  <si>
+    <t>山本開智</t>
+  </si>
+  <si>
+    <t>秋山吏乃翔</t>
+  </si>
+  <si>
+    <t>藤田大輝</t>
+  </si>
+  <si>
+    <t>佐野亮太郎</t>
+  </si>
+  <si>
+    <t>須田樹</t>
+  </si>
+  <si>
+    <t>前川聖成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">立石吏玖 </t>
+  </si>
+  <si>
+    <t>虎井蓮</t>
+  </si>
+  <si>
+    <t>藤原聡士</t>
+  </si>
+  <si>
+    <t>梶田琥太郎</t>
+  </si>
+  <si>
+    <t>水口日嵩</t>
+  </si>
+  <si>
+    <t>杉山彰吾</t>
+  </si>
+  <si>
+    <t>北垣十磨</t>
+  </si>
+  <si>
+    <t>高木龍之介</t>
+  </si>
+  <si>
+    <t>山田創太郎</t>
+  </si>
+  <si>
+    <t>芦谷泰芽</t>
+  </si>
+  <si>
+    <t>金山勢大</t>
+  </si>
+  <si>
+    <t>三宅航士朗</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +2870,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2130,13 +3026,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2206,193 +3139,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2446,10 +3215,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF0000FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2498,14 +3303,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FFFFFFFF"/>
       </font>
@@ -2546,66 +3343,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF0000FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="8"/>
-          <bgColor theme="8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3035,7 +3772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E04C86-53A8-4C49-AB0F-61EBA36494D7}">
-  <dimension ref="A1:C553"/>
+  <dimension ref="A1:C897"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
     <row r="1" spans="1:3" ht="21" thickBot="1">
@@ -6001,7 +6738,7 @@
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="24" t="s">
+      <c r="A366" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B366" s="19" t="s">
@@ -6009,7 +6746,7 @@
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="24" t="s">
+      <c r="A367" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B367" s="19" t="s">
@@ -6017,7 +6754,7 @@
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="24" t="s">
+      <c r="A368" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B368" s="19" t="s">
@@ -6025,7 +6762,7 @@
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="24" t="s">
+      <c r="A369" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B369" s="19" t="s">
@@ -6033,7 +6770,7 @@
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="24" t="s">
+      <c r="A370" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B370" s="19" t="s">
@@ -6041,7 +6778,7 @@
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="24" t="s">
+      <c r="A371" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B371" s="19" t="s">
@@ -6049,7 +6786,7 @@
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="24" t="s">
+      <c r="A372" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B372" s="19" t="s">
@@ -6057,7 +6794,7 @@
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="24" t="s">
+      <c r="A373" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B373" s="19" t="s">
@@ -6065,7 +6802,7 @@
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="24" t="s">
+      <c r="A374" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B374" s="19" t="s">
@@ -6073,7 +6810,7 @@
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="24" t="s">
+      <c r="A375" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B375" s="19" t="s">
@@ -6081,7 +6818,7 @@
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="24" t="s">
+      <c r="A376" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B376" s="19" t="s">
@@ -6089,7 +6826,7 @@
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="24" t="s">
+      <c r="A377" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B377" s="19" t="s">
@@ -6097,7 +6834,7 @@
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="24" t="s">
+      <c r="A378" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B378" s="19" t="s">
@@ -6105,7 +6842,7 @@
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="24" t="s">
+      <c r="A379" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B379" s="19" t="s">
@@ -6113,7 +6850,7 @@
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="24" t="s">
+      <c r="A380" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B380" s="19" t="s">
@@ -6121,7 +6858,7 @@
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="24" t="s">
+      <c r="A381" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B381" s="19" t="s">
@@ -6129,7 +6866,7 @@
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="24" t="s">
+      <c r="A382" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B382" s="19" t="s">
@@ -6137,7 +6874,7 @@
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="24" t="s">
+      <c r="A383" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B383" s="19" t="s">
@@ -6145,7 +6882,7 @@
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="24" t="s">
+      <c r="A384" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B384" s="19" t="s">
@@ -6153,7 +6890,7 @@
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="24" t="s">
+      <c r="A385" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B385" s="19" t="s">
@@ -6161,7 +6898,7 @@
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="24" t="s">
+      <c r="A386" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B386" s="19" t="s">
@@ -6169,7 +6906,7 @@
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="24" t="s">
+      <c r="A387" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B387" s="19" t="s">
@@ -6177,7 +6914,7 @@
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="24" t="s">
+      <c r="A388" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B388" s="19" t="s">
@@ -6185,7 +6922,7 @@
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="24" t="s">
+      <c r="A389" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B389" s="19" t="s">
@@ -6193,7 +6930,7 @@
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="24" t="s">
+      <c r="A390" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B390" s="19" t="s">
@@ -6201,7 +6938,7 @@
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="24" t="s">
+      <c r="A391" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B391" s="20" t="s">
@@ -6209,7 +6946,7 @@
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="24" t="s">
+      <c r="A392" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B392" s="20" t="s">
@@ -6217,7 +6954,7 @@
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="24" t="s">
+      <c r="A393" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B393" s="20" t="s">
@@ -6225,7 +6962,7 @@
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="24" t="s">
+      <c r="A394" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B394" s="20" t="s">
@@ -6233,7 +6970,7 @@
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="24" t="s">
+      <c r="A395" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B395" s="20" t="s">
@@ -6241,7 +6978,7 @@
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="24" t="s">
+      <c r="A396" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B396" s="20" t="s">
@@ -6249,7 +6986,7 @@
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="24" t="s">
+      <c r="A397" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B397" s="20" t="s">
@@ -6257,7 +6994,7 @@
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="24" t="s">
+      <c r="A398" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B398" s="20" t="s">
@@ -6265,7 +7002,7 @@
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="24" t="s">
+      <c r="A399" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B399" s="20" t="s">
@@ -6273,7 +7010,7 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="24" t="s">
+      <c r="A400" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B400" s="20" t="s">
@@ -6281,7 +7018,7 @@
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="24" t="s">
+      <c r="A401" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B401" s="21" t="s">
@@ -6289,7 +7026,7 @@
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="24" t="s">
+      <c r="A402" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B402" s="21" t="s">
@@ -6297,7 +7034,7 @@
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="24" t="s">
+      <c r="A403" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B403" s="21" t="s">
@@ -6305,7 +7042,7 @@
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="24" t="s">
+      <c r="A404" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B404" s="21" t="s">
@@ -6313,7 +7050,7 @@
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="24" t="s">
+      <c r="A405" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B405" s="21" t="s">
@@ -6321,7 +7058,7 @@
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="24" t="s">
+      <c r="A406" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B406" s="21" t="s">
@@ -6329,7 +7066,7 @@
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="24" t="s">
+      <c r="A407" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B407" s="21" t="s">
@@ -6337,7 +7074,7 @@
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="24" t="s">
+      <c r="A408" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B408" s="21" t="s">
@@ -6345,7 +7082,7 @@
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="24" t="s">
+      <c r="A409" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B409" s="21" t="s">
@@ -6353,7 +7090,7 @@
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="24" t="s">
+      <c r="A410" s="23" t="s">
         <v>557</v>
       </c>
       <c r="B410" s="21" t="s">
@@ -6361,7 +7098,7 @@
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="24" t="s">
+      <c r="A411" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B411" s="21" t="s">
@@ -6369,7 +7106,7 @@
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="24" t="s">
+      <c r="A412" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B412" s="21" t="s">
@@ -6377,7 +7114,7 @@
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="24" t="s">
+      <c r="A413" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B413" s="21" t="s">
@@ -6385,7 +7122,7 @@
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="24" t="s">
+      <c r="A414" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B414" s="21" t="s">
@@ -6393,7 +7130,7 @@
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="24" t="s">
+      <c r="A415" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B415" s="21" t="s">
@@ -6401,7 +7138,7 @@
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="24" t="s">
+      <c r="A416" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B416" s="21" t="s">
@@ -6409,7 +7146,7 @@
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="24" t="s">
+      <c r="A417" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B417" s="21" t="s">
@@ -6417,7 +7154,7 @@
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="24" t="s">
+      <c r="A418" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B418" s="21" t="s">
@@ -6425,7 +7162,7 @@
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="24" t="s">
+      <c r="A419" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B419" s="21" t="s">
@@ -6433,7 +7170,7 @@
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="24" t="s">
+      <c r="A420" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B420" s="21" t="s">
@@ -6441,7 +7178,7 @@
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="24" t="s">
+      <c r="A421" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B421" s="21" t="s">
@@ -6449,7 +7186,7 @@
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="24" t="s">
+      <c r="A422" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B422" s="21" t="s">
@@ -6457,7 +7194,7 @@
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="24" t="s">
+      <c r="A423" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B423" s="21" t="s">
@@ -6465,7 +7202,7 @@
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="24" t="s">
+      <c r="A424" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B424" s="21" t="s">
@@ -6473,7 +7210,7 @@
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="24" t="s">
+      <c r="A425" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B425" s="21" t="s">
@@ -6481,7 +7218,7 @@
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="24" t="s">
+      <c r="A426" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B426" s="22" t="s">
@@ -6489,7 +7226,7 @@
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="24" t="s">
+      <c r="A427" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B427" s="22" t="s">
@@ -6497,7 +7234,7 @@
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="24" t="s">
+      <c r="A428" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B428" s="22" t="s">
@@ -6505,7 +7242,7 @@
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="24" t="s">
+      <c r="A429" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B429" s="22" t="s">
@@ -6513,7 +7250,7 @@
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="24" t="s">
+      <c r="A430" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B430" s="22" t="s">
@@ -6521,7 +7258,7 @@
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="24" t="s">
+      <c r="A431" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B431" s="22" t="s">
@@ -6529,7 +7266,7 @@
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="24" t="s">
+      <c r="A432" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B432" s="20" t="s">
@@ -6537,7 +7274,7 @@
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="24" t="s">
+      <c r="A433" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B433" s="22" t="s">
@@ -6545,7 +7282,7 @@
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="24" t="s">
+      <c r="A434" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B434" s="22" t="s">
@@ -6553,7 +7290,7 @@
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="24" t="s">
+      <c r="A435" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B435" s="22" t="s">
@@ -6561,7 +7298,7 @@
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="24" t="s">
+      <c r="A436" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B436" s="22" t="s">
@@ -6569,7 +7306,7 @@
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="24" t="s">
+      <c r="A437" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B437" s="22" t="s">
@@ -6577,7 +7314,7 @@
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="24" t="s">
+      <c r="A438" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B438" s="22" t="s">
@@ -6585,7 +7322,7 @@
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="24" t="s">
+      <c r="A439" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B439" s="22" t="s">
@@ -6593,7 +7330,7 @@
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="24" t="s">
+      <c r="A440" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B440" s="22" t="s">
@@ -6601,7 +7338,7 @@
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="24" t="s">
+      <c r="A441" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B441" s="21" t="s">
@@ -6609,7 +7346,7 @@
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="24" t="s">
+      <c r="A442" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B442" s="21" t="s">
@@ -6617,7 +7354,7 @@
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="24" t="s">
+      <c r="A443" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B443" s="21" t="s">
@@ -6625,7 +7362,7 @@
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="24" t="s">
+      <c r="A444" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B444" s="21" t="s">
@@ -6633,7 +7370,7 @@
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="24" t="s">
+      <c r="A445" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B445" s="21" t="s">
@@ -6641,7 +7378,7 @@
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="24" t="s">
+      <c r="A446" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B446" s="21" t="s">
@@ -6649,7 +7386,7 @@
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="24" t="s">
+      <c r="A447" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B447" s="21" t="s">
@@ -6657,7 +7394,7 @@
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="24" t="s">
+      <c r="A448" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B448" s="21" t="s">
@@ -6665,7 +7402,7 @@
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="24" t="s">
+      <c r="A449" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B449" s="21" t="s">
@@ -6673,7 +7410,7 @@
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="24" t="s">
+      <c r="A450" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B450" s="21" t="s">
@@ -6681,7 +7418,7 @@
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="24" t="s">
+      <c r="A451" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B451" s="21" t="s">
@@ -6689,7 +7426,7 @@
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="24" t="s">
+      <c r="A452" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B452" s="21" t="s">
@@ -6697,7 +7434,7 @@
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="24" t="s">
+      <c r="A453" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B453" s="21" t="s">
@@ -6705,7 +7442,7 @@
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="24" t="s">
+      <c r="A454" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B454" s="21" t="s">
@@ -6713,7 +7450,7 @@
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="24" t="s">
+      <c r="A455" s="23" t="s">
         <v>558</v>
       </c>
       <c r="B455" s="21" t="s">
@@ -6721,7 +7458,7 @@
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="24" t="s">
+      <c r="A456" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B456" s="21" t="s">
@@ -6729,7 +7466,7 @@
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="24" t="s">
+      <c r="A457" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B457" s="21" t="s">
@@ -6737,7 +7474,7 @@
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="24" t="s">
+      <c r="A458" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B458" s="21" t="s">
@@ -6745,7 +7482,7 @@
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="24" t="s">
+      <c r="A459" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B459" s="21" t="s">
@@ -6753,7 +7490,7 @@
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="24" t="s">
+      <c r="A460" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B460" s="21" t="s">
@@ -6761,7 +7498,7 @@
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="24" t="s">
+      <c r="A461" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B461" s="21" t="s">
@@ -6769,7 +7506,7 @@
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="24" t="s">
+      <c r="A462" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B462" s="21" t="s">
@@ -6777,7 +7514,7 @@
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="24" t="s">
+      <c r="A463" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B463" s="21" t="s">
@@ -6785,7 +7522,7 @@
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="24" t="s">
+      <c r="A464" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B464" s="21" t="s">
@@ -6793,7 +7530,7 @@
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="24" t="s">
+      <c r="A465" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B465" s="21" t="s">
@@ -6801,7 +7538,7 @@
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="24" t="s">
+      <c r="A466" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B466" s="21" t="s">
@@ -6809,7 +7546,7 @@
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="24" t="s">
+      <c r="A467" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B467" s="21" t="s">
@@ -6817,7 +7554,7 @@
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="24" t="s">
+      <c r="A468" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B468" s="21" t="s">
@@ -6825,7 +7562,7 @@
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="24" t="s">
+      <c r="A469" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B469" s="21" t="s">
@@ -6833,7 +7570,7 @@
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="24" t="s">
+      <c r="A470" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B470" s="21" t="s">
@@ -6841,7 +7578,7 @@
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="24" t="s">
+      <c r="A471" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B471" s="21" t="s">
@@ -6849,7 +7586,7 @@
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="24" t="s">
+      <c r="A472" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B472" s="21" t="s">
@@ -6857,7 +7594,7 @@
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="24" t="s">
+      <c r="A473" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B473" s="21" t="s">
@@ -6865,7 +7602,7 @@
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="24" t="s">
+      <c r="A474" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B474" s="21" t="s">
@@ -6873,7 +7610,7 @@
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="24" t="s">
+      <c r="A475" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B475" s="21" t="s">
@@ -6881,7 +7618,7 @@
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="24" t="s">
+      <c r="A476" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B476" s="21" t="s">
@@ -6889,7 +7626,7 @@
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="24" t="s">
+      <c r="A477" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B477" s="21" t="s">
@@ -6897,7 +7634,7 @@
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="24" t="s">
+      <c r="A478" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B478" s="21" t="s">
@@ -6905,7 +7642,7 @@
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="24" t="s">
+      <c r="A479" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B479" s="21" t="s">
@@ -6913,7 +7650,7 @@
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="24" t="s">
+      <c r="A480" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B480" s="21" t="s">
@@ -6921,7 +7658,7 @@
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="24" t="s">
+      <c r="A481" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B481" s="21" t="s">
@@ -6929,7 +7666,7 @@
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="24" t="s">
+      <c r="A482" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B482" s="21" t="s">
@@ -6937,7 +7674,7 @@
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="24" t="s">
+      <c r="A483" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B483" s="21" t="s">
@@ -6945,7 +7682,7 @@
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="24" t="s">
+      <c r="A484" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B484" s="21" t="s">
@@ -6953,7 +7690,7 @@
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="24" t="s">
+      <c r="A485" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B485" s="21" t="s">
@@ -6961,7 +7698,7 @@
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="24" t="s">
+      <c r="A486" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B486" s="21" t="s">
@@ -6969,7 +7706,7 @@
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="24" t="s">
+      <c r="A487" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B487" s="21" t="s">
@@ -6977,7 +7714,7 @@
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="24" t="s">
+      <c r="A488" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B488" s="21" t="s">
@@ -6985,7 +7722,7 @@
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="24" t="s">
+      <c r="A489" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B489" s="21" t="s">
@@ -6993,7 +7730,7 @@
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="24" t="s">
+      <c r="A490" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B490" s="21" t="s">
@@ -7001,7 +7738,7 @@
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="24" t="s">
+      <c r="A491" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B491" s="21" t="s">
@@ -7009,7 +7746,7 @@
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="24" t="s">
+      <c r="A492" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B492" s="21" t="s">
@@ -7017,7 +7754,7 @@
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="24" t="s">
+      <c r="A493" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B493" s="21" t="s">
@@ -7025,7 +7762,7 @@
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="24" t="s">
+      <c r="A494" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B494" s="21" t="s">
@@ -7033,7 +7770,7 @@
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="24" t="s">
+      <c r="A495" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B495" s="21" t="s">
@@ -7041,7 +7778,7 @@
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="24" t="s">
+      <c r="A496" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B496" s="21" t="s">
@@ -7049,7 +7786,7 @@
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="24" t="s">
+      <c r="A497" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B497" s="21" t="s">
@@ -7057,7 +7794,7 @@
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="24" t="s">
+      <c r="A498" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B498" s="21" t="s">
@@ -7065,7 +7802,7 @@
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="24" t="s">
+      <c r="A499" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B499" s="21" t="s">
@@ -7073,7 +7810,7 @@
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="24" t="s">
+      <c r="A500" s="23" t="s">
         <v>559</v>
       </c>
       <c r="B500" s="21" t="s">
@@ -7081,7 +7818,7 @@
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="24" t="s">
+      <c r="A501" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B501" s="21" t="s">
@@ -7089,7 +7826,7 @@
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="24" t="s">
+      <c r="A502" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B502" s="21" t="s">
@@ -7097,7 +7834,7 @@
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="24" t="s">
+      <c r="A503" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B503" s="21" t="s">
@@ -7105,7 +7842,7 @@
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="24" t="s">
+      <c r="A504" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B504" s="21" t="s">
@@ -7113,7 +7850,7 @@
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="24" t="s">
+      <c r="A505" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B505" s="21" t="s">
@@ -7121,7 +7858,7 @@
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="24" t="s">
+      <c r="A506" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B506" s="21" t="s">
@@ -7129,7 +7866,7 @@
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="24" t="s">
+      <c r="A507" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B507" s="21" t="s">
@@ -7137,7 +7874,7 @@
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="24" t="s">
+      <c r="A508" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B508" s="21" t="s">
@@ -7145,7 +7882,7 @@
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="24" t="s">
+      <c r="A509" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B509" s="21" t="s">
@@ -7153,7 +7890,7 @@
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="24" t="s">
+      <c r="A510" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B510" s="21" t="s">
@@ -7161,7 +7898,7 @@
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="24" t="s">
+      <c r="A511" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B511" s="21" t="s">
@@ -7169,7 +7906,7 @@
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="24" t="s">
+      <c r="A512" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B512" s="21" t="s">
@@ -7177,7 +7914,7 @@
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="24" t="s">
+      <c r="A513" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B513" s="21" t="s">
@@ -7185,7 +7922,7 @@
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="24" t="s">
+      <c r="A514" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B514" s="21" t="s">
@@ -7193,7 +7930,7 @@
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="24" t="s">
+      <c r="A515" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B515" s="21" t="s">
@@ -7201,7 +7938,7 @@
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="24" t="s">
+      <c r="A516" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B516" s="22" t="s">
@@ -7209,7 +7946,7 @@
       </c>
     </row>
     <row r="517" spans="1:2">
-      <c r="A517" s="24" t="s">
+      <c r="A517" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B517" s="22" t="s">
@@ -7217,7 +7954,7 @@
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="24" t="s">
+      <c r="A518" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B518" s="22" t="s">
@@ -7225,7 +7962,7 @@
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="24" t="s">
+      <c r="A519" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B519" s="22" t="s">
@@ -7233,7 +7970,7 @@
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="24" t="s">
+      <c r="A520" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B520" s="22" t="s">
@@ -7241,7 +7978,7 @@
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="24" t="s">
+      <c r="A521" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B521" s="22" t="s">
@@ -7249,7 +7986,7 @@
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="24" t="s">
+      <c r="A522" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B522" s="22" t="s">
@@ -7257,7 +7994,7 @@
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="24" t="s">
+      <c r="A523" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B523" s="22" t="s">
@@ -7265,7 +8002,7 @@
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="24" t="s">
+      <c r="A524" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B524" s="22" t="s">
@@ -7273,7 +8010,7 @@
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="24" t="s">
+      <c r="A525" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B525" s="22" t="s">
@@ -7281,7 +8018,7 @@
       </c>
     </row>
     <row r="526" spans="1:2">
-      <c r="A526" s="24" t="s">
+      <c r="A526" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B526" s="21" t="s">
@@ -7289,7 +8026,7 @@
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="24" t="s">
+      <c r="A527" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B527" s="21" t="s">
@@ -7297,7 +8034,7 @@
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="24" t="s">
+      <c r="A528" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B528" s="21" t="s">
@@ -7305,7 +8042,7 @@
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="24" t="s">
+      <c r="A529" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B529" s="21" t="s">
@@ -7313,7 +8050,7 @@
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="24" t="s">
+      <c r="A530" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B530" s="21" t="s">
@@ -7321,7 +8058,7 @@
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="24" t="s">
+      <c r="A531" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B531" s="21" t="s">
@@ -7329,7 +8066,7 @@
       </c>
     </row>
     <row r="532" spans="1:2">
-      <c r="A532" s="24" t="s">
+      <c r="A532" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B532" s="21" t="s">
@@ -7337,7 +8074,7 @@
       </c>
     </row>
     <row r="533" spans="1:2">
-      <c r="A533" s="24" t="s">
+      <c r="A533" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B533" s="21" t="s">
@@ -7345,7 +8082,7 @@
       </c>
     </row>
     <row r="534" spans="1:2">
-      <c r="A534" s="24" t="s">
+      <c r="A534" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B534" s="21" t="s">
@@ -7353,7 +8090,7 @@
       </c>
     </row>
     <row r="535" spans="1:2">
-      <c r="A535" s="24" t="s">
+      <c r="A535" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B535" s="21" t="s">
@@ -7361,7 +8098,7 @@
       </c>
     </row>
     <row r="536" spans="1:2">
-      <c r="A536" s="24" t="s">
+      <c r="A536" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B536" s="21" t="s">
@@ -7369,7 +8106,7 @@
       </c>
     </row>
     <row r="537" spans="1:2">
-      <c r="A537" s="24" t="s">
+      <c r="A537" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B537" s="21" t="s">
@@ -7377,7 +8114,7 @@
       </c>
     </row>
     <row r="538" spans="1:2">
-      <c r="A538" s="24" t="s">
+      <c r="A538" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B538" s="21" t="s">
@@ -7385,7 +8122,7 @@
       </c>
     </row>
     <row r="539" spans="1:2">
-      <c r="A539" s="24" t="s">
+      <c r="A539" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B539" s="21" t="s">
@@ -7393,7 +8130,7 @@
       </c>
     </row>
     <row r="540" spans="1:2">
-      <c r="A540" s="24" t="s">
+      <c r="A540" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B540" s="21" t="s">
@@ -7401,7 +8138,7 @@
       </c>
     </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="24" t="s">
+      <c r="A541" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B541" s="21" t="s">
@@ -7409,7 +8146,7 @@
       </c>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="24" t="s">
+      <c r="A542" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B542" s="21" t="s">
@@ -7417,7 +8154,7 @@
       </c>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="24" t="s">
+      <c r="A543" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B543" s="21" t="s">
@@ -7425,7 +8162,7 @@
       </c>
     </row>
     <row r="544" spans="1:2">
-      <c r="A544" s="24" t="s">
+      <c r="A544" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B544" s="21" t="s">
@@ -7433,7 +8170,7 @@
       </c>
     </row>
     <row r="545" spans="1:2">
-      <c r="A545" s="24" t="s">
+      <c r="A545" s="23" t="s">
         <v>560</v>
       </c>
       <c r="B545" s="21" t="s">
@@ -7441,92 +8178,2898 @@
       </c>
     </row>
     <row r="546" spans="1:2">
-      <c r="B546" s="23"/>
+      <c r="A546" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="B546" s="25" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="547" spans="1:2">
-      <c r="B547" s="23"/>
+      <c r="A547" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B547" s="27" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="548" spans="1:2">
-      <c r="B548" s="23"/>
+      <c r="A548" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B548" s="27" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="549" spans="1:2">
-      <c r="B549" s="23"/>
+      <c r="A549" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B549" s="27" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="550" spans="1:2">
-      <c r="B550" s="23"/>
+      <c r="A550" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B550" s="27" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="551" spans="1:2">
-      <c r="B551" s="23"/>
+      <c r="A551" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B551" s="27" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="552" spans="1:2">
-      <c r="B552" s="23"/>
+      <c r="A552" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B552" s="27" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="553" spans="1:2">
-      <c r="B553" s="23"/>
+      <c r="A553" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B553" s="27" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B554" s="27" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B555" s="27" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B556" s="27" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B557" s="27" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B558" s="27" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B559" s="27" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B560" s="27" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B561" s="27" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B562" s="27" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B563" s="27" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B564" s="27" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B565" s="27" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B566" s="27" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B567" s="27" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B568" s="27" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B569" s="27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B570" s="27" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B571" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B572" s="27" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B573" s="27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B574" s="27" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B575" s="27" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B576" s="27" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B577" s="27" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B578" s="27" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B579" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B580" s="27" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B581" s="27" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B582" s="27" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B583" s="27" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B584" s="27" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B585" s="27" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B586" s="27" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B587" s="27" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B588" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B589" s="27" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B590" s="27" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B591" s="27" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B592" s="27" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B593" s="27" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B594" s="27" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B595" s="27" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B596" s="27" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B597" s="27" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B598" s="27" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B599" s="27" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B600" s="27" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B601" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B602" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B603" s="27" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B604" s="27" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B605" s="27" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B606" s="28" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B607" s="28" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B608" s="28" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B609" s="28" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B610" s="28" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B611" s="28" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B612" s="28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B613" s="28" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B614" s="28" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B615" s="28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B616" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B617" s="28" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B618" s="28" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B619" s="28" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B620" s="28" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B621" s="28" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B622" s="28" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B623" s="28" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B624" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B625" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B626" s="28" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B627" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B628" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B629" s="28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B630" s="28" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B631" s="28" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B632" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B633" s="28" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B634" s="28" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B635" s="28" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B636" s="28" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B637" s="28" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B638" s="28" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B639" s="28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B640" s="28" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B641" s="28" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B642" s="28" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B643" s="28" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B644" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B645" s="28" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B646" s="28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B647" s="28" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B648" s="28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B649" s="28" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B650" s="28" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B651" s="28" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B652" s="28" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B653" s="28" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B654" s="28" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B655" s="28" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B656" s="28" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B657" s="28" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B658" s="28" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B659" s="28" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B660" s="28" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B661" s="28" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B662" s="28" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B663" s="28" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B664" s="28" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="B665" s="28" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B666" s="28" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B667" s="28" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B668" s="28" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B669" s="28" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B670" s="28" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B671" s="28" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B672" s="28" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B673" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B674" s="28" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B675" s="28" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B676" s="28" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B677" s="28" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B678" s="28" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B679" s="28" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B680" s="28" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B681" s="28" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B682" s="28" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B683" s="28" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B684" s="28" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B685" s="28" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B686" s="28" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B687" s="28" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B688" s="28" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B689" s="28" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B690" s="28" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B691" s="28" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B692" s="28" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B693" s="28" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B694" s="28" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B695" s="28" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B696" s="28" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B697" s="28" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B698" s="28" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B699" s="28" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B700" s="28" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B701" s="28" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B702" s="28" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B703" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B704" s="28" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B705" s="28" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B706" s="28" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B707" s="28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B708" s="28" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B709" s="28" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B710" s="28" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B711" s="28" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B712" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B713" s="28" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B714" s="28" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B715" s="28" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B716" s="28" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B717" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B718" s="28" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B719" s="28" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B720" s="28" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B721" s="28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B722" s="28" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B723" s="28" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B724" s="28" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B725" s="28" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B726" s="27" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B727" s="27" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B728" s="27" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B729" s="27" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B730" s="27" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B731" s="27" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B732" s="27" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B733" s="27" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B734" s="27" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B735" s="27" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B736" s="27" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B737" s="27" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B738" s="27" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B739" s="27" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B740" s="27" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B741" s="27" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B742" s="27" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B743" s="27" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B744" s="27" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B745" s="27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B746" s="27" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B747" s="27" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B748" s="27" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B749" s="27" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B750" s="27" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B751" s="27" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B752" s="27" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B753" s="27" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B754" s="27" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B755" s="27" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B756" s="27" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B757" s="27" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B758" s="27" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B759" s="27" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B760" s="27" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B761" s="27" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B762" s="27" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B763" s="27" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B764" s="27" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B765" s="27" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B766" s="27" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B767" s="27" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B768" s="27" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B769" s="27" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B770" s="27" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B771" s="27" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B772" s="27" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B773" s="27" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B774" s="27" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B775" s="27" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B776" s="27" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B777" s="27" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B778" s="27" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B779" s="27" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B780" s="27" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B781" s="27" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B782" s="27" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B783" s="27" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B784" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="B785" s="27" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B786" s="19" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B787" s="19" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B788" s="19" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B789" s="19" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B790" s="19" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B791" s="19" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B792" s="19" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B793" s="19" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B794" s="19" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B795" s="19" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B796" s="19" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B797" s="19" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B798" s="19" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B799" s="19" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B800" s="19" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B801" s="19" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B802" s="19" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B803" s="19" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B804" s="19" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B805" s="19" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B806" s="19" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B807" s="19" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B808" s="19" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B809" s="19" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B810" s="19" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B811" s="19" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B812" s="19" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B813" s="19" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B814" s="21" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B815" s="21" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B816" s="21" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B817" s="21" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B818" s="21" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B819" s="21" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2">
+      <c r="A820" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B820" s="21" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2">
+      <c r="A821" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B821" s="21" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2">
+      <c r="A822" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B822" s="21" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2">
+      <c r="A823" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B823" s="21" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2">
+      <c r="A824" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B824" s="21" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2">
+      <c r="A825" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B825" s="21" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2">
+      <c r="A826" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B826" s="21" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2">
+      <c r="A827" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B827" s="21" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2">
+      <c r="A828" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B828" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2">
+      <c r="A829" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B829" s="21" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2">
+      <c r="A830" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B830" s="21" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2">
+      <c r="A831" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B831" s="21" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2">
+      <c r="A832" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B832" s="21" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2">
+      <c r="A833" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B833" s="21" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2">
+      <c r="A834" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B834" s="21" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2">
+      <c r="A835" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B835" s="21" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2">
+      <c r="A836" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B836" s="21" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2">
+      <c r="A837" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B837" s="21" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2">
+      <c r="A838" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B838" s="21" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2">
+      <c r="A839" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B839" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2">
+      <c r="A840" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B840" s="21" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2">
+      <c r="A841" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="B841" s="21" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2">
+      <c r="A842" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B842" s="20" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2">
+      <c r="A843" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B843" s="20" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2">
+      <c r="A844" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B844" s="20" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2">
+      <c r="A845" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B845" s="20" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2">
+      <c r="A846" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B846" s="20" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2">
+      <c r="A847" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B847" s="20" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2">
+      <c r="A848" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B848" s="20" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2">
+      <c r="A849" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B849" s="20" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2">
+      <c r="A850" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B850" s="20" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2">
+      <c r="A851" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B851" s="20" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2">
+      <c r="A852" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B852" s="20" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2">
+      <c r="A853" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B853" s="20" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2">
+      <c r="A854" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B854" s="20" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2">
+      <c r="A855" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B855" s="20" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2">
+      <c r="A856" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B856" s="20" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B857" s="20" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2">
+      <c r="A858" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B858" s="20" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2">
+      <c r="A859" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B859" s="20" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2">
+      <c r="A860" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B860" s="20" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2">
+      <c r="A861" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B861" s="20" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B862" s="20" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B863" s="20" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2">
+      <c r="A864" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B864" s="20" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2">
+      <c r="A865" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B865" s="20" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2">
+      <c r="A866" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B866" s="20" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2">
+      <c r="A867" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B867" s="20" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2">
+      <c r="A868" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B868" s="20" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2">
+      <c r="A869" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="B869" s="20" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2">
+      <c r="A870" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B870" s="19" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2">
+      <c r="A871" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B871" s="19" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2">
+      <c r="A872" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B872" s="19" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2">
+      <c r="A873" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B873" s="19" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2">
+      <c r="A874" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B874" s="19" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2">
+      <c r="A875" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B875" s="19" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2">
+      <c r="A876" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B876" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2">
+      <c r="A877" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B877" s="19" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2">
+      <c r="A878" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B878" s="19" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2">
+      <c r="A879" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B879" s="19" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2">
+      <c r="A880" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B880" s="19" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2">
+      <c r="A881" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B881" s="19" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2">
+      <c r="A882" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B882" s="19" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2">
+      <c r="A883" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B883" s="19" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2">
+      <c r="A884" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B884" s="19" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2">
+      <c r="A885" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B885" s="19" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2">
+      <c r="A886" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B886" s="19" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2">
+      <c r="A887" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B887" s="19" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2">
+      <c r="A888" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B888" s="19" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2">
+      <c r="A889" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B889" s="19" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2">
+      <c r="A890" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B890" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2">
+      <c r="A891" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B891" s="19" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2">
+      <c r="A892" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B892" s="19" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2">
+      <c r="A893" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B893" s="19" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2">
+      <c r="A894" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B894" s="19" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2">
+      <c r="A895" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B895" s="19" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2">
+      <c r="A896" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B896" s="19" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2">
+      <c r="A897" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="B897" s="19" t="s">
+        <v>536</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B2:B344">
-    <cfRule type="cellIs" dxfId="45" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="43" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="44" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="45" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="46" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="42">
+    <cfRule type="expression" dxfId="21" priority="47">
       <formula>COUNTIF(INDIRECT("綱引き!A:Z"),B2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C21 C43:C63">
-    <cfRule type="cellIs" dxfId="40" priority="101" operator="equal">
+  <conditionalFormatting sqref="B401:B425">
+    <cfRule type="cellIs" dxfId="20" priority="14" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="103" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="104" operator="equal">
-      <formula>"黒団"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B401:B425">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"赤団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
-      <formula>"青団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>"黄団"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B441:B515">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>"青団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"黄団"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B526:B545">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="7" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C21 C43:C63">
+    <cfRule type="cellIs" dxfId="8" priority="106" operator="equal">
+      <formula>"赤団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="107" operator="equal">
+      <formula>"青団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="108" operator="equal">
+      <formula>"黄団"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="109" operator="equal">
+      <formula>"黒団"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B786:B841 B870:B897">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"赤団"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
@@ -7538,6 +11081,9 @@
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"黒団"</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>COUNTIF(INDIRECT("女子棒取り!A:Z"),B786)&gt;0</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
